--- a/results/Int All Data -0.9/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_10_permute.xlsx
@@ -440,227 +440,227 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8755656799956792</v>
+        <v>0.8788943798697515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8666711437822103</v>
+        <v>0.8783350957534204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8612708896526042</v>
+        <v>0.8773821097305488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8663399793626293</v>
+        <v>0.8770644477229248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8672684478479997</v>
+        <v>0.877851851536006</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8273730844341353</v>
+        <v>0.8757042573815554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8317197951044518</v>
+        <v>0.8676351449306261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8355697591453968</v>
+        <v>0.8688922905491644</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8343616486018608</v>
+        <v>0.8737712805118978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8330284630844057</v>
+        <v>0.8737712805118978</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8333461250920295</v>
+        <v>0.857065243654577</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8428354780848748</v>
+        <v>0.8583739116345309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8428219756729176</v>
+        <v>0.8367618799905625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8422626915565865</v>
+        <v>0.8356568141698575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8387303895232654</v>
+        <v>0.8366098001927291</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8420345718598364</v>
+        <v>0.831095486214748</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8313861433984576</v>
+        <v>0.8160893319575087</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8345627634746965</v>
+        <v>0.8171318602912541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8342070815176142</v>
+        <v>0.8180848463141258</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8354127047747372</v>
+        <v>0.8070046959967481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8382336428938938</v>
+        <v>0.8084139214131199</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8281064785993877</v>
+        <v>0.8084139214131199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8303681326022132</v>
+        <v>0.8120602832948159</v>
       </c>
     </row>
     <row r="25">
@@ -670,1317 +670,1317 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8303681326022132</v>
+        <v>0.8139662553405593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8303681326022132</v>
+        <v>0.8159482672852192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8303681326022132</v>
+        <v>0.8179057616923782</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.834294136542075</v>
+        <v>0.8124674876133137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8398734752934287</v>
+        <v>0.7870030046419871</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8373186768204806</v>
+        <v>0.795463331713044</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8419180247250482</v>
+        <v>0.796785502104955</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8341285543322844</v>
+        <v>0.8068501289125015</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8273435923238077</v>
+        <v>0.7974343285321599</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8259073620835216</v>
+        <v>0.7973828061707444</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8224510999491172</v>
+        <v>0.8198877736370381</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8188427580168794</v>
+        <v>0.8190598625880854</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8215116163382028</v>
+        <v>0.808449454076165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8216882136735373</v>
+        <v>0.7980426477234934</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8309519342560455</v>
+        <v>0.7957269840728391</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8335067327289938</v>
+        <v>0.7992838036436614</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8212294869936241</v>
+        <v>0.8025119460813157</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8149302564889749</v>
+        <v>0.8100217744159141</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8032663045177649</v>
+        <v>0.8100217744159141</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7987675140496149</v>
+        <v>0.8092723905522913</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7865442779620739</v>
+        <v>0.8092723905522913</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.77822004099048</v>
+        <v>0.804189798430309</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7908149487334737</v>
+        <v>0.799131723845828</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7882736526724827</v>
+        <v>0.8057646060564714</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7832180653744147</v>
+        <v>0.8236542359198269</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7925443234438825</v>
+        <v>0.7887629374426148</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7918709794791765</v>
+        <v>0.7886488775942397</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7880210154382314</v>
+        <v>0.7897539434149448</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8062553121331253</v>
+        <v>0.7904788097410664</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8143354397095985</v>
+        <v>0.7964003280375452</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8112483619442337</v>
+        <v>0.7931096481129314</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8106130379289858</v>
+        <v>0.7891321218116542</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.810295375921362</v>
+        <v>0.7935143651450159</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7731424234413242</v>
+        <v>0.821582681664293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7744130714718198</v>
+        <v>0.8047465952602271</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7641718473289386</v>
+        <v>0.7613324322249986</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7769298499953097</v>
+        <v>0.7469726171085509</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8233575381833997</v>
+        <v>0.7453843070704314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8236371802415652</v>
+        <v>0.7528045930941558</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7961121581402488</v>
+        <v>0.7474178413765069</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.796785502104955</v>
+        <v>0.7449145652649742</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7958325160820833</v>
+        <v>0.7487019918189597</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7963918001984144</v>
+        <v>0.7491337136749585</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7917654474699323</v>
+        <v>0.7675176028812726</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7919310296797228</v>
+        <v>0.7721304531977975</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8024138759313111</v>
+        <v>0.7673275031339809</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.810659585717575</v>
+        <v>0.7758283374409092</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8047515698330534</v>
+        <v>0.7823176676928499</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8201514259968333</v>
+        <v>0.7821140655336011</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7495508671391089</v>
+        <v>0.7821140655336011</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7410120128827222</v>
+        <v>0.7796438347987003</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6454657479341309</v>
+        <v>0.7784602417926655</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6451480859265071</v>
+        <v>0.7819435087509843</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6451861058759654</v>
+        <v>0.7888425306078359</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6268512517446537</v>
+        <v>0.7961597719087294</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.646570813754836</v>
+        <v>0.779959009519911</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6455798077825059</v>
+        <v>0.7900531284377852</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.640852897617606</v>
+        <v>0.7892142022632885</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6453001657243405</v>
+        <v>0.7732500874103511</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6191378212508065</v>
+        <v>0.7744827154913883</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6131022431059527</v>
+        <v>0.7552094437290535</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6166100276017726</v>
+        <v>0.7077967901213511</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6221353567052977</v>
+        <v>0.7126292322954954</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6217796747482156</v>
+        <v>0.7141169848971969</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6100126780541746</v>
+        <v>0.7035851035706062</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5800298616500231</v>
+        <v>0.6995425524959564</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5609076037056304</v>
+        <v>0.6788760450156202</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5609076037056304</v>
+        <v>0.6788760450156202</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5571852019250175</v>
+        <v>0.6769185506084614</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5591291939202192</v>
+        <v>0.6794598466694524</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.552064589853577</v>
+        <v>0.6486736367538497</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5605654241605054</v>
+        <v>0.6132560995369383</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5605654241605054</v>
+        <v>0.5950353052540017</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5605654241605054</v>
+        <v>0.5943999812387539</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5446443038298525</v>
+        <v>0.5905990522728113</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.537530664688208</v>
+        <v>0.6810090707782221</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.537530664688208</v>
+        <v>0.6796268501857647</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5622947988709142</v>
+        <v>0.6415454292203565</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5311283894607279</v>
+        <v>0.6415454292203565</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5299718012786073</v>
+        <v>0.6415454292203565</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5217125890803862</v>
+        <v>0.6415834491698149</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5220302510880102</v>
+        <v>0.641265787162191</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5230457745978413</v>
+        <v>0.6409861451040254</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5202468667297727</v>
+        <v>0.6407065030458599</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5178196305171566</v>
+        <v>0.5980218255829488</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5197256025628999</v>
+        <v>0.5903353999130161</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4979234711716398</v>
+        <v>0.6037042090571337</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5032476854023292</v>
+        <v>0.5887225723373954</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.494882941194864</v>
+        <v>0.5788295682923571</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.494882941194864</v>
+        <v>0.5616868350062111</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4934467109545779</v>
+        <v>0.5669669887347245</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4937263530127434</v>
+        <v>0.5565516545429221</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4783460398136383</v>
+        <v>0.5565516545429221</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5042166611235712</v>
+        <v>0.5525030629155545</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5038229592170307</v>
+        <v>0.5285973978720199</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5043062034344451</v>
+        <v>0.5104782270053925</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5043062034344451</v>
+        <v>0.5013825759190879</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5045858454926107</v>
+        <v>0.4768501146994363</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5049035075002345</v>
+        <v>0.4947777645122502</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5047379252904439</v>
+        <v>0.4947777645122502</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5070375992427278</v>
+        <v>0.503628240223543</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5070375992427278</v>
+        <v>0.503628240223543</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5068339970834791</v>
+        <v>0.5137973330604424</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5073282564264374</v>
+        <v>0.5068983112035907</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5073282564264374</v>
+        <v>0.5154236630480202</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5021451068680374</v>
+        <v>0.4923668733246349</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4948879157676903</v>
+        <v>0.4894833977185188</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4994652334211701</v>
+        <v>0.503864177106163</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.495398164809019</v>
+        <v>0.4844246124807768</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4965927729405979</v>
+        <v>0.4851114588574401</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4995927956815022</v>
+        <v>0.4851874987563568</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4995927956815022</v>
+        <v>0.485429120865064</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4995927956815022</v>
+        <v>0.485429120865064</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4993511735727951</v>
+        <v>0.4790598910142159</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4993891935222534</v>
+        <v>0.4739772988922337</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4996553331684618</v>
+        <v>0.4731383727177371</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4996553331684618</v>
+        <v>0.4791629357370469</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4991205665896318</v>
+        <v>0.4799638419620852</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4991205665896318</v>
+        <v>0.5014962804408324</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.500442736981543</v>
+        <v>0.5015588179277919</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4996798507059629</v>
+        <v>0.5006708566782929</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5002391348222941</v>
+        <v>0.4974292118286814</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5004807569310012</v>
+        <v>0.5013442006429991</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5004807569310012</v>
+        <v>0.5014987677272456</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4992481288499641</v>
+        <v>0.5009014636614562</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5011676033076645</v>
+        <v>0.501536787676704</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997203579418344</v>
+        <v>0.5041921435860701</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5042301635355284</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.5041921435860701</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.5057939560361466</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003176620076238</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4997203579418344</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
